--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:44</t>
+    <t xml:space="preserve">2026-09-09 23:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:44</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:32</t>
+    <t xml:space="preserve">2026-09-23 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:05</t>
+    <t xml:space="preserve">2026-10-02 14:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:54</t>
+    <t xml:space="preserve">2026-10-05 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
